--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2028-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2028-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A144E25-7A8F-4FCC-8C33-7031355E61F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC64324A-538E-434F-ACF9-BF711240F360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{41DFA77C-C75A-4E6A-8BFB-FAA0AA76E052}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{59C4C4D8-FCEC-40A9-8985-090A6AAF3BAD}"/>
   </bookViews>
   <sheets>
     <sheet name="2028-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1481,25 +1481,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D6B0F3-6245-4C37-B2F1-C39BD0DACF56}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{769C9FC8-A07E-4C04-99BF-5A345BD6DE15}">
   <dimension ref="A1:R58"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1527,7 +1527,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1557,7 +1557,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1653,7 +1653,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>26</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>26</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="37">
         <v>2024</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="39">
         <v>2023</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>26</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>26</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>26</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2022</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="39">
         <v>2021</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="37">
         <v>2020</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2019</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="37">
         <v>2018</v>
       </c>
@@ -3203,7 +3203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="39">
         <v>2017</v>
       </c>
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="37">
         <v>2016</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="39">
         <v>2015</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
         <v>2014</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <v>2013</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="37">
         <v>2012</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="39">
         <v>2011</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>2010</v>
       </c>
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="39">
         <v>2009</v>
       </c>
@@ -3689,7 +3689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="37">
         <v>2008</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="39">
         <v>2007</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="37">
         <v>2006</v>
       </c>
@@ -3851,7 +3851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="39">
         <v>2005</v>
       </c>
@@ -3905,7 +3905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="37">
         <v>2004</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="39">
         <v>2003</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="37">
         <v>2002</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="39">
         <v>2001</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="37">
         <v>2000</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="39">
         <v>1999</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="37">
         <v>1998</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="39">
         <v>1997</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="37">
         <v>1996</v>
       </c>
@@ -4391,7 +4391,7 @@
         <v>4.09</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="39">
         <v>1995</v>
       </c>
@@ -4445,7 +4445,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="37">
         <v>1994</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="39">
         <v>1993</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="37" t="s">
         <v>46</v>
       </c>
